--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_26_31_dec.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_26_31_dec.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <x:workbookPr codeName="ЭтаКнига"/>
   <x:bookViews>
-    <x:workbookView xWindow="32767" yWindow="32767" windowWidth="23040" windowHeight="8748" firstSheet="0" activeTab="1"/>
+    <x:workbookView xWindow="32760" yWindow="32760" windowWidth="23040" windowHeight="8745" firstSheet="0" activeTab="1"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Основное для всех " sheetId="1" r:id="rId3"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
   <x:si>
     <x:t>УТВЕРЖДАЮ</x:t>
   </x:si>
@@ -305,6 +305,11 @@
 Основной корпус-Аудитория 403</x:t>
   </x:si>
   <x:si>
+    <x:t>Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-Аудитория 33</x:t>
+  </x:si>
+  <x:si>
     <x:t>Основы предпринимательской деятельности 
 Криворучко А.В. 
 Производственный корпус-Аудитория 37а</x:t>
@@ -413,6 +418,11 @@
 Основной корпус-Аудитория 105</x:t>
   </x:si>
   <x:si>
+    <x:t>Иностранный язык в профессиональной деятельности 
+Цибарт П.А. 
+Производственный корпус-Аудитория 38</x:t>
+  </x:si>
+  <x:si>
     <x:t>Анализ финансово - хозяйственной деятельности 
 Кравченко С.О. 
 Основной корпус-Аудитория 304</x:t>
@@ -495,6 +505,11 @@
     <x:t>Математика 
 Зеленина С.В. 
 Производственный корпус-Аудитория 35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.01.02 Организация, принципы построения и функционирования компьютерных сетей 
+Плотникова Ю.А. 
+Основной корпус-Аудитория 405</x:t>
   </x:si>
   <x:si>
     <x:t>Организация депозитных операций банка 
@@ -830,6 +845,11 @@
 Производственный корпус-Аудитория 38</x:t>
   </x:si>
   <x:si>
+    <x:t>Основы электротехники 
+Сагдиев Т.Ф. 
+Производственный корпус-Аудитория 47</x:t>
+  </x:si>
+  <x:si>
     <x:t>Информационные технологии в профессиональной деятельности 
 Беляев А.А. 
 Производственный корпус-Аудитория 48</x:t>
@@ -990,6 +1010,11 @@
 Производственный корпус-</x:t>
   </x:si>
   <x:si>
+    <x:t>Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-О125</x:t>
+  </x:si>
+  <x:si>
     <x:t>Организация бухгалтерского учета в банках 
 Силкина М.Г. 
 Производственный корпус-Аудитория 38</x:t>
@@ -1048,11 +1073,11 @@
     <x:numFmt numFmtId="7" formatCode="#,##0.00\ &quot;₽&quot;;\-#,##0.00\ &quot;₽&quot;"/>
     <x:numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
     <x:numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
-    <x:numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <x:numFmt numFmtId="41" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;\ _₽_-;_-@_-"/>
     <x:numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <x:numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <x:numFmt numFmtId="164" formatCode="_-* #,##0\ _₽_-;\-* #,##0\ _₽_-;_-* &quot;-&quot;\ _₽_-;_-@_-"/>
-    <x:numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <x:numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <x:numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <x:numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <x:numFmt numFmtId="166" formatCode="#,##0&quot;р.&quot;;\-#,##0&quot;р.&quot;"/>
     <x:numFmt numFmtId="167" formatCode="#,##0&quot;р.&quot;;[Red]\-#,##0&quot;р.&quot;"/>
     <x:numFmt numFmtId="168" formatCode="#,##0.00&quot;р.&quot;;\-#,##0.00&quot;р.&quot;"/>
@@ -1066,7 +1091,7 @@
     <x:numFmt numFmtId="176" formatCode="&quot;Вкл&quot;;&quot;Вкл&quot;;&quot;Выкл&quot;"/>
     <x:numFmt numFmtId="177" formatCode="[$€-2]\ ###,000_);[Red]\([$€-2]\ ###,000\)"/>
   </x:numFmts>
-  <x:fonts count="47">
+  <x:fonts count="30">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial Cyr"/>
@@ -1125,12 +1150,6 @@
       <x:sz val="10"/>
       <x:name val="Arial"/>
       <x:family val="0"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:sz val="11"/>
@@ -1245,138 +1264,17 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:i/>
       <x:sz val="18"/>
       <x:color rgb="FF0000FF"/>
       <x:name val="Arial"/>
       <x:family val="0"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF006100"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFF0000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:i/>
-      <x:sz val="11"/>
-      <x:color rgb="FF7F7F7F"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C0006"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF9C6500"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="18"/>
-      <x:color theme="3"/>
-      <x:name val="Cambria"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="13"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="15"/>
-      <x:color theme="3"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFA7D00"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F3F"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF3F3F76"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="0"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:scheme val="minor"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
@@ -1386,7 +1284,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1419,25 +1317,25 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.7999799847602844"/>
+        <x:fgColor indexed="27"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.7999799847602844"/>
+        <x:fgColor indexed="47"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.5999900102615356"/>
+        <x:fgColor indexed="44"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.5999900102615356"/>
+        <x:fgColor indexed="29"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1449,31 +1347,13 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="7" tint="0.5999900102615356"/>
+        <x:fgColor indexed="51"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.5999900102615356"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9" tint="0.5999900102615356"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="4" tint="0.39998000860214233"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="5" tint="0.39998000860214233"/>
+        <x:fgColor indexed="30"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1485,7 +1365,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="8" tint="0.39998000860214233"/>
+        <x:fgColor indexed="49"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1497,85 +1377,49 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="4"/>
+        <x:fgColor indexed="62"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="5"/>
+        <x:fgColor indexed="10"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="6"/>
+        <x:fgColor indexed="57"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor theme="7"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="8"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor theme="9"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFCC99"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF2F2F2"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA5A5A5"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFEB9C"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFC7CE"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFCC"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFC6EFCE"/>
+        <x:fgColor indexed="53"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor indexed="22"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="55"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="43"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor indexed="26"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1590,30 +1434,30 @@
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF7F7F7F"/>
+        <x:color indexed="23"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1627,7 +1471,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="thick">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1641,7 +1485,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="thick">
-        <x:color theme="4" tint="0.49998000264167786"/>
+        <x:color indexed="22"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1655,7 +1499,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="medium">
-        <x:color theme="4" tint="0.39998000860214233"/>
+        <x:color indexed="30"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1666,38 +1510,38 @@
         <x:color indexed="0"/>
       </x:right>
       <x:top style="thin">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:top>
       <x:bottom style="double">
-        <x:color theme="4"/>
+        <x:color indexed="62"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:left>
       <x:right style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:right>
       <x:top style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:top>
       <x:bottom style="double">
-        <x:color rgb="FF3F3F3F"/>
+        <x:color indexed="63"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:left>
       <x:right style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:right>
       <x:top style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFB2B2B2"/>
+        <x:color indexed="22"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1711,7 +1555,7 @@
         <x:color indexed="0"/>
       </x:top>
       <x:bottom style="double">
-        <x:color rgb="FFFF8001"/>
+        <x:color indexed="52"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -1790,58 +1634,58 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="44" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="43" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="42" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="41" fillId="26" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="13" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="40" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="39" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="37" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="36" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <x:alignment/>
       <x:protection/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="173" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <x:xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <x:xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1860,35 +1704,35 @@
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment/>
     </x:xf>
@@ -1925,54 +1769,54 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment vertical="top" wrapText="1"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" xfId="53" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="53" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90"/>
       <x:protection/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment/>
     </x:xf>
     <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment/>
@@ -2002,31 +1846,47 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="12" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="12" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="11" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="32" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="90" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2036,6 +1896,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -2490,7 +2354,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{4ca43acf-63d3-4e66-bb12-d0da1e0ecd35}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{927b76a8-7f6d-40f4-b41b-fa9f8041de83}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr codeName="Лист1">
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -2591,6 +2455,13 @@
       <x:c r="AD2" s="28" t="s"/>
       <x:c r="AE2" s="28" t="s"/>
       <x:c r="AF2" s="28" t="s"/>
+      <x:c r="AG2" s="26" t="s"/>
+      <x:c r="AH2" s="26" t="s"/>
+      <x:c r="AI2" s="26" t="s"/>
+      <x:c r="AJ2" s="26" t="s"/>
+      <x:c r="AK2" s="26" t="s"/>
+      <x:c r="AL2" s="26" t="s"/>
+      <x:c r="AM2" s="26" t="s"/>
       <x:c r="AN2" s="26" t="s"/>
       <x:c r="AO2" s="26" t="s"/>
       <x:c r="AP2" s="26" t="s"/>
@@ -2635,6 +2506,13 @@
       <x:c r="AD3" s="31" t="s"/>
       <x:c r="AE3" s="31" t="s"/>
       <x:c r="AF3" s="31" t="s"/>
+      <x:c r="AG3" s="26" t="s"/>
+      <x:c r="AH3" s="26" t="s"/>
+      <x:c r="AI3" s="26" t="s"/>
+      <x:c r="AJ3" s="26" t="s"/>
+      <x:c r="AK3" s="26" t="s"/>
+      <x:c r="AL3" s="26" t="s"/>
+      <x:c r="AM3" s="26" t="s"/>
       <x:c r="AN3" s="26" t="s"/>
       <x:c r="AO3" s="26" t="s"/>
       <x:c r="AP3" s="26" t="s"/>
@@ -2677,6 +2555,13 @@
       <x:c r="AD4" s="31" t="s"/>
       <x:c r="AE4" s="31" t="s"/>
       <x:c r="AF4" s="31" t="s"/>
+      <x:c r="AG4" s="26" t="s"/>
+      <x:c r="AH4" s="26" t="s"/>
+      <x:c r="AI4" s="26" t="s"/>
+      <x:c r="AJ4" s="26" t="s"/>
+      <x:c r="AK4" s="26" t="s"/>
+      <x:c r="AL4" s="26" t="s"/>
+      <x:c r="AM4" s="26" t="s"/>
       <x:c r="AN4" s="26" t="s"/>
       <x:c r="AO4" s="26" t="s"/>
       <x:c r="AP4" s="26" t="s"/>
@@ -2687,1854 +2572,1868 @@
       <x:c r="AU4" s="26" t="s"/>
     </x:row>
     <x:row r="5" spans="1:47" s="7" customFormat="1" ht="24.6" customHeight="1">
-      <x:c r="A5" s="12" t="s">
+      <x:c r="A5" s="32" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="s">
+      <x:c r="B5" s="32" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s">
+      <x:c r="C5" s="33" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D5" s="13" t="s">
+      <x:c r="D5" s="33" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E5" s="13" t="s">
+      <x:c r="E5" s="33" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="F5" s="13" t="s">
+      <x:c r="F5" s="33" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G5" s="13" t="s">
+      <x:c r="G5" s="33" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H5" s="13" t="s">
+      <x:c r="H5" s="33" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I5" s="13" t="s">
+      <x:c r="I5" s="33" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J5" s="13" t="s">
+      <x:c r="J5" s="33" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K5" s="13" t="s">
+      <x:c r="K5" s="33" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L5" s="13" t="s">
+      <x:c r="L5" s="33" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M5" s="13" t="s">
+      <x:c r="M5" s="33" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="N5" s="13" t="s">
+      <x:c r="N5" s="33" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="O5" s="13" t="s">
+      <x:c r="O5" s="33" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="P5" s="13" t="s">
+      <x:c r="P5" s="33" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="Q5" s="13" t="s">
+      <x:c r="Q5" s="33" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="R5" s="13" t="s">
+      <x:c r="R5" s="33" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="S5" s="13" t="s">
+      <x:c r="S5" s="33" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="T5" s="13" t="s">
+      <x:c r="T5" s="33" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="U5" s="13" t="s">
+      <x:c r="U5" s="33" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="V5" s="13" t="s">
+      <x:c r="V5" s="33" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="W5" s="13" t="s">
+      <x:c r="W5" s="33" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="X5" s="13" t="s">
+      <x:c r="X5" s="33" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="Y5" s="13" t="s">
+      <x:c r="Y5" s="33" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="Z5" s="13" t="s">
+      <x:c r="Z5" s="33" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="AA5" s="13" t="s">
+      <x:c r="AA5" s="33" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AB5" s="13" t="s">
+      <x:c r="AB5" s="33" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="AC5" s="13" t="s">
+      <x:c r="AC5" s="33" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="AD5" s="13" t="s">
+      <x:c r="AD5" s="33" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="AE5" s="13" t="s">
+      <x:c r="AE5" s="33" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="AF5" s="13" t="s">
+      <x:c r="AF5" s="33" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="AG5" s="13" t="s">
+      <x:c r="AG5" s="33" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="AH5" s="13" t="s">
+      <x:c r="AH5" s="33" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="AI5" s="13" t="s">
+      <x:c r="AI5" s="33" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="AJ5" s="13" t="s">
+      <x:c r="AJ5" s="33" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="AK5" s="13" t="s">
+      <x:c r="AK5" s="33" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="AL5" s="13" t="s">
+      <x:c r="AL5" s="33" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="AM5" s="13" t="s">
+      <x:c r="AM5" s="33" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="AN5" s="13" t="s">
+      <x:c r="AN5" s="33" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AO5" s="13" t="s">
+      <x:c r="AO5" s="33" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="AP5" s="13" t="s">
+      <x:c r="AP5" s="33" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="AQ5" s="13" t="s">
+      <x:c r="AQ5" s="33" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="AR5" s="13" t="s">
+      <x:c r="AR5" s="33" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="AS5" s="13" t="s">
+      <x:c r="AS5" s="33" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="AT5" s="13" t="s">
+      <x:c r="AT5" s="33" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="AU5" s="13" t="s">
+      <x:c r="AU5" s="33" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:47" s="7" customFormat="1" ht="52.8" customHeight="1">
-      <x:c r="A6" s="32" t="s">
+    <x:row r="6" spans="1:47" s="7" customFormat="1" ht="51" customHeight="1">
+      <x:c r="A6" s="34" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="s">
+      <x:c r="B6" s="35" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="s">
+      <x:c r="C6" s="36" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D6" s="34" t="s">
+      <x:c r="D6" s="36" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="E6" s="34" t="s">
+      <x:c r="E6" s="36" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F6" s="34" t="s">
+      <x:c r="F6" s="36" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G6" s="34" t="s">
+      <x:c r="G6" s="36" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H6" s="34" t="s"/>
-      <x:c r="I6" s="34" t="s">
+      <x:c r="H6" s="36" t="s"/>
+      <x:c r="I6" s="36" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J6" s="34" t="s">
+      <x:c r="J6" s="36" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K6" s="34" t="s"/>
-      <x:c r="L6" s="34" t="s"/>
-      <x:c r="M6" s="34" t="s">
+      <x:c r="K6" s="36" t="s"/>
+      <x:c r="L6" s="36" t="s"/>
+      <x:c r="M6" s="36" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N6" s="34" t="s"/>
-      <x:c r="O6" s="34" t="s"/>
-      <x:c r="P6" s="34" t="s">
+      <x:c r="N6" s="36" t="s"/>
+      <x:c r="O6" s="36" t="s"/>
+      <x:c r="P6" s="36" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="Q6" s="34" t="s"/>
-      <x:c r="R6" s="34" t="s">
+      <x:c r="Q6" s="36" t="s"/>
+      <x:c r="R6" s="36" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="S6" s="34" t="s"/>
-      <x:c r="T6" s="34" t="s"/>
-      <x:c r="U6" s="34" t="s">
+      <x:c r="S6" s="36" t="s"/>
+      <x:c r="T6" s="36" t="s"/>
+      <x:c r="U6" s="36" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="V6" s="34" t="s"/>
-      <x:c r="W6" s="34" t="s"/>
-      <x:c r="X6" s="34" t="s">
+      <x:c r="V6" s="36" t="s"/>
+      <x:c r="W6" s="36" t="s"/>
+      <x:c r="X6" s="36" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="Y6" s="34" t="s"/>
-      <x:c r="Z6" s="34" t="s"/>
-      <x:c r="AA6" s="34" t="s"/>
-      <x:c r="AB6" s="34" t="s"/>
-      <x:c r="AC6" s="34" t="s"/>
-      <x:c r="AD6" s="34" t="s"/>
-      <x:c r="AE6" s="34" t="s">
+      <x:c r="Y6" s="36" t="s"/>
+      <x:c r="Z6" s="36" t="s"/>
+      <x:c r="AA6" s="36" t="s"/>
+      <x:c r="AB6" s="36" t="s"/>
+      <x:c r="AC6" s="36" t="s"/>
+      <x:c r="AD6" s="36" t="s"/>
+      <x:c r="AE6" s="36" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="AF6" s="34" t="s"/>
-      <x:c r="AG6" s="34" t="s"/>
-      <x:c r="AH6" s="34" t="s">
+      <x:c r="AF6" s="36" t="s"/>
+      <x:c r="AG6" s="36" t="s"/>
+      <x:c r="AH6" s="36" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="AI6" s="34" t="s"/>
-      <x:c r="AJ6" s="34" t="s"/>
-      <x:c r="AK6" s="34" t="s">
+      <x:c r="AI6" s="36" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="AL6" s="34" t="s"/>
-      <x:c r="AM6" s="34" t="s"/>
-      <x:c r="AN6" s="34" t="s"/>
-      <x:c r="AO6" s="34" t="s"/>
-      <x:c r="AP6" s="34" t="s"/>
-      <x:c r="AQ6" s="34" t="s"/>
-      <x:c r="AR6" s="34" t="s">
+      <x:c r="AJ6" s="36" t="s"/>
+      <x:c r="AK6" s="36" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="AS6" s="34" t="s"/>
-      <x:c r="AT6" s="34" t="s">
+      <x:c r="AL6" s="36" t="s"/>
+      <x:c r="AM6" s="36" t="s"/>
+      <x:c r="AN6" s="36" t="s"/>
+      <x:c r="AO6" s="36" t="s"/>
+      <x:c r="AP6" s="36" t="s"/>
+      <x:c r="AQ6" s="36" t="s"/>
+      <x:c r="AR6" s="36" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="AU6" s="34" t="s"/>
+      <x:c r="AS6" s="36" t="s"/>
+      <x:c r="AT6" s="36" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="AU6" s="36" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:47" s="7" customFormat="1" ht="92.4" customHeight="1">
-      <x:c r="A7" s="35" t="s"/>
-      <x:c r="B7" s="33" t="s">
+    <x:row r="7" spans="1:47" s="7" customFormat="1" ht="89.25" customHeight="1">
+      <x:c r="A7" s="37" t="s"/>
+      <x:c r="B7" s="35" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C7" s="45" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D7" s="36" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E7" s="36" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F7" s="36" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G7" s="36" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H7" s="36" t="s"/>
+      <x:c r="I7" s="36" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J7" s="36" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K7" s="36" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L7" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M7" s="36" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N7" s="36" t="s"/>
+      <x:c r="O7" s="45" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="Q7" s="36" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="R7" s="36" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="S7" s="36" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="T7" s="36" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="U7" s="36" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="V7" s="36" t="s"/>
+      <x:c r="W7" s="36" t="s"/>
+      <x:c r="X7" s="36" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Y7" s="36" t="s"/>
+      <x:c r="Z7" s="36" t="s"/>
+      <x:c r="AA7" s="36" t="s"/>
+      <x:c r="AB7" s="36" t="s"/>
+      <x:c r="AC7" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AD7" s="36" t="s"/>
+      <x:c r="AE7" s="36" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="AF7" s="36" t="s"/>
+      <x:c r="AG7" s="36" t="s"/>
+      <x:c r="AH7" s="36" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AI7" s="36" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="AJ7" s="36" t="s"/>
+      <x:c r="AK7" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AL7" s="36" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="AM7" s="45" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="AN7" s="36" t="s"/>
+      <x:c r="AO7" s="36" t="s"/>
+      <x:c r="AP7" s="36" t="s"/>
+      <x:c r="AQ7" s="36" t="s"/>
+      <x:c r="AR7" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AS7" s="36" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="AT7" s="36" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="AU7" s="36" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:47" s="7" customFormat="1" ht="76.5" customHeight="1">
+      <x:c r="A8" s="37" t="s"/>
+      <x:c r="B8" s="35" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C8" s="45" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D8" s="36" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E8" s="36" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F8" s="36" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G8" s="36" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H8" s="36" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="I8" s="36" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J8" s="36" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="K8" s="36" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="L8" s="36" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="M8" s="36" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="N8" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O8" s="45" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="P8" s="45" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="Q8" s="36" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R8" s="36" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="S8" s="36" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="T8" s="36" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="U8" s="36" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="V8" s="36" t="s"/>
+      <x:c r="W8" s="36" t="s"/>
+      <x:c r="X8" s="36" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="Y8" s="36" t="s"/>
+      <x:c r="Z8" s="36" t="s"/>
+      <x:c r="AA8" s="36" t="s"/>
+      <x:c r="AB8" s="36" t="s"/>
+      <x:c r="AC8" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AD8" s="36" t="s"/>
+      <x:c r="AE8" s="36" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="AF8" s="36" t="s"/>
+      <x:c r="AG8" s="36" t="s"/>
+      <x:c r="AH8" s="36" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AI8" s="36" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AJ8" s="36" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="AK8" s="36" t="s"/>
+      <x:c r="AL8" s="36" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="AM8" s="45" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="AN8" s="36" t="s"/>
+      <x:c r="AO8" s="36" t="s"/>
+      <x:c r="AP8" s="36" t="s"/>
+      <x:c r="AQ8" s="36" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AR8" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AS8" s="36" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="AT8" s="36" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AU8" s="36" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:47" ht="89.25" customHeight="1">
+      <x:c r="A9" s="37" t="s"/>
+      <x:c r="B9" s="35" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C9" s="45" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D9" s="36" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E9" s="36" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F9" s="36" t="s"/>
+      <x:c r="G9" s="36" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H9" s="36" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I9" s="36" t="s"/>
+      <x:c r="J9" s="36" t="s"/>
+      <x:c r="K9" s="36" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L9" s="36" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="M9" s="36" t="s"/>
+      <x:c r="N9" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="P9" s="45" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="Q9" s="36" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="R9" s="36" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="S9" s="36" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="T9" s="36" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="U9" s="36" t="s"/>
+      <x:c r="V9" s="36" t="s"/>
+      <x:c r="W9" s="36" t="s"/>
+      <x:c r="X9" s="36" t="s"/>
+      <x:c r="Y9" s="36" t="s"/>
+      <x:c r="Z9" s="36" t="s"/>
+      <x:c r="AA9" s="36" t="s"/>
+      <x:c r="AB9" s="36" t="s"/>
+      <x:c r="AC9" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AD9" s="36" t="s"/>
+      <x:c r="AE9" s="36" t="s"/>
+      <x:c r="AF9" s="36" t="s"/>
+      <x:c r="AG9" s="36" t="s"/>
+      <x:c r="AH9" s="36" t="s"/>
+      <x:c r="AI9" s="36" t="s"/>
+      <x:c r="AJ9" s="36" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="AK9" s="36" t="s"/>
+      <x:c r="AL9" s="36" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AM9" s="45" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="AN9" s="36" t="s"/>
+      <x:c r="AO9" s="36" t="s"/>
+      <x:c r="AP9" s="36" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AQ9" s="36" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="AR9" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AS9" s="36" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="AT9" s="36" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="AU9" s="36" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C7" s="36" t="s">
+    </x:row>
+    <x:row r="10" spans="1:47" ht="89.25" customHeight="1">
+      <x:c r="A10" s="37" t="s"/>
+      <x:c r="B10" s="35" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C10" s="45" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D10" s="36" t="s"/>
+      <x:c r="E10" s="36" t="s"/>
+      <x:c r="F10" s="36" t="s"/>
+      <x:c r="G10" s="36" t="s"/>
+      <x:c r="H10" s="36" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="I10" s="36" t="s"/>
+      <x:c r="J10" s="36" t="s"/>
+      <x:c r="K10" s="36" t="s"/>
+      <x:c r="L10" s="36" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M10" s="36" t="s"/>
+      <x:c r="N10" s="36" t="s"/>
+      <x:c r="O10" s="45" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="P10" s="45" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="Q10" s="36" t="s"/>
+      <x:c r="R10" s="36" t="s"/>
+      <x:c r="S10" s="36" t="s"/>
+      <x:c r="T10" s="36" t="s"/>
+      <x:c r="U10" s="36" t="s"/>
+      <x:c r="V10" s="36" t="s"/>
+      <x:c r="W10" s="36" t="s"/>
+      <x:c r="X10" s="36" t="s"/>
+      <x:c r="Y10" s="36" t="s"/>
+      <x:c r="Z10" s="36" t="s"/>
+      <x:c r="AA10" s="36" t="s"/>
+      <x:c r="AB10" s="36" t="s"/>
+      <x:c r="AC10" s="36" t="s"/>
+      <x:c r="AD10" s="36" t="s"/>
+      <x:c r="AE10" s="36" t="s"/>
+      <x:c r="AF10" s="36" t="s"/>
+      <x:c r="AG10" s="36" t="s"/>
+      <x:c r="AH10" s="36" t="s"/>
+      <x:c r="AI10" s="36" t="s"/>
+      <x:c r="AJ10" s="36" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AK10" s="36" t="s"/>
+      <x:c r="AL10" s="36" t="s"/>
+      <x:c r="AM10" s="45" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="AN10" s="36" t="s"/>
+      <x:c r="AO10" s="36" t="s"/>
+      <x:c r="AP10" s="36" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="AQ10" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AR10" s="36" t="s"/>
+      <x:c r="AS10" s="36" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="AT10" s="36" t="s"/>
+      <x:c r="AU10" s="36" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A11" s="37" t="s"/>
+      <x:c r="B11" s="35" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C11" s="36" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D11" s="36" t="s"/>
+      <x:c r="E11" s="36" t="s"/>
+      <x:c r="F11" s="36" t="s"/>
+      <x:c r="G11" s="36" t="s"/>
+      <x:c r="H11" s="38" t="s"/>
+      <x:c r="I11" s="36" t="s"/>
+      <x:c r="J11" s="36" t="s"/>
+      <x:c r="K11" s="36" t="s"/>
+      <x:c r="L11" s="36" t="s"/>
+      <x:c r="M11" s="36" t="s"/>
+      <x:c r="N11" s="36" t="s"/>
+      <x:c r="O11" s="45" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="P11" s="45" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="Q11" s="36" t="s"/>
+      <x:c r="R11" s="36" t="s"/>
+      <x:c r="S11" s="36" t="s"/>
+      <x:c r="T11" s="36" t="s"/>
+      <x:c r="U11" s="36" t="s"/>
+      <x:c r="V11" s="36" t="s"/>
+      <x:c r="W11" s="36" t="s"/>
+      <x:c r="X11" s="36" t="s"/>
+      <x:c r="Y11" s="36" t="s"/>
+      <x:c r="Z11" s="36" t="s"/>
+      <x:c r="AA11" s="36" t="s"/>
+      <x:c r="AB11" s="36" t="s"/>
+      <x:c r="AC11" s="36" t="s"/>
+      <x:c r="AD11" s="36" t="s"/>
+      <x:c r="AE11" s="36" t="s"/>
+      <x:c r="AF11" s="36" t="s"/>
+      <x:c r="AG11" s="36" t="s"/>
+      <x:c r="AH11" s="36" t="s"/>
+      <x:c r="AI11" s="36" t="s"/>
+      <x:c r="AJ11" s="36" t="s"/>
+      <x:c r="AK11" s="36" t="s"/>
+      <x:c r="AL11" s="36" t="s"/>
+      <x:c r="AM11" s="36" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="AN11" s="36" t="s"/>
+      <x:c r="AO11" s="36" t="s"/>
+      <x:c r="AP11" s="36" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AQ11" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AR11" s="36" t="s"/>
+      <x:c r="AS11" s="36" t="s"/>
+      <x:c r="AT11" s="36" t="s"/>
+      <x:c r="AU11" s="36" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:47" ht="76.5" customHeight="1">
+      <x:c r="A12" s="39" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C12" s="40" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D12" s="40" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E12" s="40" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F12" s="40" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G12" s="40" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H12" s="40" t="s"/>
+      <x:c r="I12" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J12" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K12" s="40" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="L12" s="40" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M12" s="40" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="N12" s="40" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="O12" s="45" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="P12" s="40" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="Q12" s="40" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="R12" s="40" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="S12" s="40" t="s"/>
+      <x:c r="T12" s="40" t="s"/>
+      <x:c r="U12" s="40" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="V12" s="40" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="W12" s="40" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="X12" s="40" t="s"/>
+      <x:c r="Y12" s="40" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="Z12" s="40" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AA12" s="40" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="AB12" s="40" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AC12" s="40" t="s"/>
+      <x:c r="AD12" s="40" t="s"/>
+      <x:c r="AE12" s="40" t="s"/>
+      <x:c r="AF12" s="40" t="s"/>
+      <x:c r="AG12" s="40" t="s"/>
+      <x:c r="AH12" s="40" t="s"/>
+      <x:c r="AI12" s="40" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="AJ12" s="40" t="s"/>
+      <x:c r="AK12" s="40" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AL12" s="40" t="s"/>
+      <x:c r="AM12" s="40" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="AN12" s="40" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AO12" s="40" t="s"/>
+      <x:c r="AP12" s="40" t="s"/>
+      <x:c r="AQ12" s="40" t="s"/>
+      <x:c r="AR12" s="40" t="s"/>
+      <x:c r="AS12" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AT12" s="40" t="s"/>
+      <x:c r="AU12" s="40" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:47" ht="89.25" customHeight="1">
+      <x:c r="A13" s="41" t="s"/>
+      <x:c r="B13" s="33" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E7" s="34" t="s">
+      <x:c r="C13" s="40" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E13" s="40" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F13" s="40" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G13" s="40" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H13" s="40" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="F7" s="34" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="s">
+      <x:c r="I13" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J13" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K13" s="40" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="L13" s="40" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="M13" s="40" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="N13" s="40" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="O13" s="40" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="P13" s="40" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="Q13" s="40" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="R13" s="40" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="S13" s="40" t="s"/>
+      <x:c r="T13" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="U13" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="V13" s="40" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="W13" s="40" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="X13" s="40" t="s"/>
+      <x:c r="Y13" s="40" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="Z13" s="40" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AA13" s="40" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="AB13" s="40" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AC13" s="40" t="s"/>
+      <x:c r="AD13" s="40" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="AE13" s="40" t="s"/>
+      <x:c r="AF13" s="40" t="s"/>
+      <x:c r="AG13" s="40" t="s"/>
+      <x:c r="AH13" s="40" t="s"/>
+      <x:c r="AI13" s="40" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AJ13" s="40" t="s"/>
+      <x:c r="AK13" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AL13" s="40" t="s"/>
+      <x:c r="AM13" s="40" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="AN13" s="40" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AO13" s="40" t="s"/>
+      <x:c r="AP13" s="40" t="s"/>
+      <x:c r="AQ13" s="40" t="s"/>
+      <x:c r="AR13" s="40" t="s"/>
+      <x:c r="AS13" s="40" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AT13" s="40" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="AU13" s="40" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:47" ht="76.5" customHeight="1">
+      <x:c r="A14" s="41" t="s"/>
+      <x:c r="B14" s="33" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C14" s="40" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D14" s="40" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E14" s="40" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F14" s="40" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G14" s="40" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H14" s="40" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="I14" s="40" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J14" s="40" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="K14" s="40" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="L14" s="40" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M14" s="40" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="N14" s="40" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O14" s="40" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="P14" s="40" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="Q14" s="40" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="R14" s="40" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="S14" s="40" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="T14" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="U14" s="40" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="V14" s="40" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="W14" s="40" t="s"/>
+      <x:c r="X14" s="40" t="s"/>
+      <x:c r="Y14" s="40" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="Z14" s="40" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AA14" s="40" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="AB14" s="40" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AC14" s="40" t="s"/>
+      <x:c r="AD14" s="40" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="AE14" s="40" t="s"/>
+      <x:c r="AF14" s="40" t="s"/>
+      <x:c r="AG14" s="40" t="s"/>
+      <x:c r="AH14" s="40" t="s"/>
+      <x:c r="AI14" s="40" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="AJ14" s="40" t="s"/>
+      <x:c r="AK14" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AL14" s="40" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="AM14" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AN14" s="40" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AO14" s="40" t="s"/>
+      <x:c r="AP14" s="40" t="s"/>
+      <x:c r="AQ14" s="40" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="AR14" s="40" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AS14" s="40" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AT14" s="40" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="AU14" s="40" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A15" s="41" t="s"/>
+      <x:c r="B15" s="33" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="s"/>
+      <x:c r="E15" s="40" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G15" s="40" t="s"/>
+      <x:c r="H15" s="40" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="s"/>
+      <x:c r="J15" s="40" t="s"/>
+      <x:c r="K15" s="40" t="s"/>
+      <x:c r="L15" s="40" t="s"/>
+      <x:c r="M15" s="40" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="N15" s="40" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="O15" s="40" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="P15" s="40" t="s"/>
+      <x:c r="Q15" s="40" t="s"/>
+      <x:c r="R15" s="40" t="s"/>
+      <x:c r="S15" s="40" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="T15" s="40" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="U15" s="40" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="V15" s="40" t="s"/>
+      <x:c r="W15" s="40" t="s"/>
+      <x:c r="X15" s="40" t="s"/>
+      <x:c r="Y15" s="40" t="s"/>
+      <x:c r="Z15" s="40" t="s"/>
+      <x:c r="AA15" s="40" t="s"/>
+      <x:c r="AB15" s="40" t="s"/>
+      <x:c r="AC15" s="40" t="s"/>
+      <x:c r="AD15" s="40" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="AE15" s="40" t="s"/>
+      <x:c r="AF15" s="40" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AG15" s="40" t="s"/>
+      <x:c r="AH15" s="40" t="s"/>
+      <x:c r="AI15" s="40" t="s"/>
+      <x:c r="AJ15" s="40" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="AK15" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AL15" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AM15" s="40" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AN15" s="40" t="s"/>
+      <x:c r="AO15" s="40" t="s"/>
+      <x:c r="AP15" s="40" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AQ15" s="40" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="AR15" s="40" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AS15" s="40" t="s"/>
+      <x:c r="AT15" s="40" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="AU15" s="40" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A16" s="41" t="s"/>
+      <x:c r="B16" s="33" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="s"/>
+      <x:c r="D16" s="40" t="s"/>
+      <x:c r="E16" s="40" t="s"/>
+      <x:c r="F16" s="40" t="s"/>
+      <x:c r="G16" s="40" t="s"/>
+      <x:c r="H16" s="40" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="I16" s="40" t="s"/>
+      <x:c r="J16" s="40" t="s"/>
+      <x:c r="K16" s="40" t="s"/>
+      <x:c r="L16" s="40" t="s"/>
+      <x:c r="M16" s="40" t="s"/>
+      <x:c r="N16" s="40" t="s"/>
+      <x:c r="O16" s="40" t="s"/>
+      <x:c r="P16" s="40" t="s"/>
+      <x:c r="Q16" s="40" t="s"/>
+      <x:c r="R16" s="40" t="s"/>
+      <x:c r="S16" s="40" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="T16" s="40" t="s"/>
+      <x:c r="U16" s="40" t="s"/>
+      <x:c r="V16" s="40" t="s"/>
+      <x:c r="W16" s="40" t="s"/>
+      <x:c r="X16" s="40" t="s"/>
+      <x:c r="Y16" s="40" t="s"/>
+      <x:c r="Z16" s="40" t="s"/>
+      <x:c r="AA16" s="40" t="s"/>
+      <x:c r="AB16" s="40" t="s"/>
+      <x:c r="AC16" s="40" t="s"/>
+      <x:c r="AD16" s="40" t="s"/>
+      <x:c r="AE16" s="40" t="s"/>
+      <x:c r="AF16" s="40" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AG16" s="40" t="s"/>
+      <x:c r="AH16" s="40" t="s"/>
+      <x:c r="AI16" s="40" t="s"/>
+      <x:c r="AJ16" s="40" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AK16" s="40" t="s"/>
+      <x:c r="AL16" s="40" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="AM16" s="40" t="s"/>
+      <x:c r="AN16" s="40" t="s"/>
+      <x:c r="AO16" s="40" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="AP16" s="40" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="AQ16" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AR16" s="40" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AS16" s="40" t="s"/>
+      <x:c r="AT16" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AU16" s="40" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A17" s="41" t="s"/>
+      <x:c r="B17" s="33" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="s"/>
+      <x:c r="D17" s="40" t="s"/>
+      <x:c r="E17" s="40" t="s"/>
+      <x:c r="F17" s="40" t="s"/>
+      <x:c r="G17" s="40" t="s"/>
+      <x:c r="H17" s="40" t="s"/>
+      <x:c r="I17" s="40" t="s"/>
+      <x:c r="J17" s="40" t="s"/>
+      <x:c r="K17" s="40" t="s"/>
+      <x:c r="L17" s="40" t="s"/>
+      <x:c r="M17" s="40" t="s"/>
+      <x:c r="N17" s="40" t="s"/>
+      <x:c r="O17" s="40" t="s"/>
+      <x:c r="P17" s="40" t="s"/>
+      <x:c r="Q17" s="40" t="s"/>
+      <x:c r="R17" s="40" t="s"/>
+      <x:c r="S17" s="40" t="s"/>
+      <x:c r="T17" s="40" t="s"/>
+      <x:c r="U17" s="40" t="s"/>
+      <x:c r="V17" s="40" t="s"/>
+      <x:c r="W17" s="40" t="s"/>
+      <x:c r="X17" s="40" t="s"/>
+      <x:c r="Y17" s="40" t="s"/>
+      <x:c r="Z17" s="40" t="s"/>
+      <x:c r="AA17" s="40" t="s"/>
+      <x:c r="AB17" s="40" t="s"/>
+      <x:c r="AC17" s="40" t="s"/>
+      <x:c r="AD17" s="40" t="s"/>
+      <x:c r="AE17" s="40" t="s"/>
+      <x:c r="AF17" s="40" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AG17" s="40" t="s"/>
+      <x:c r="AH17" s="40" t="s"/>
+      <x:c r="AI17" s="40" t="s"/>
+      <x:c r="AJ17" s="40" t="s"/>
+      <x:c r="AK17" s="40" t="s"/>
+      <x:c r="AL17" s="40" t="s"/>
+      <x:c r="AM17" s="40" t="s"/>
+      <x:c r="AN17" s="40" t="s"/>
+      <x:c r="AO17" s="40" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="AP17" s="40" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="AQ17" s="40" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AR17" s="40" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AS17" s="40" t="s"/>
+      <x:c r="AT17" s="40" t="s"/>
+      <x:c r="AU17" s="40" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:47" ht="76.5" customHeight="1">
+      <x:c r="A18" s="34" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B18" s="35" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C18" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D18" s="36" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E18" s="36" t="s"/>
+      <x:c r="F18" s="36" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H7" s="34" t="s"/>
-      <x:c r="I7" s="34" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="J7" s="34" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="K7" s="34" t="s">
+      <x:c r="G18" s="36" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H18" s="36" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I18" s="36" t="s"/>
+      <x:c r="J18" s="36" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="K18" s="36" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="L18" s="36" t="s"/>
+      <x:c r="M18" s="36" t="s"/>
+      <x:c r="N18" s="36" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="O18" s="36" t="s"/>
+      <x:c r="P18" s="36" t="s"/>
+      <x:c r="Q18" s="36" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="R18" s="36" t="s"/>
+      <x:c r="S18" s="36" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="T18" s="36" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="U18" s="36" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="V18" s="36" t="s"/>
+      <x:c r="W18" s="36" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="X18" s="36" t="s"/>
+      <x:c r="Y18" s="36" t="s"/>
+      <x:c r="Z18" s="36" t="s"/>
+      <x:c r="AA18" s="36" t="s"/>
+      <x:c r="AB18" s="36" t="s"/>
+      <x:c r="AC18" s="36" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AD18" s="36" t="s"/>
+      <x:c r="AE18" s="36" t="s"/>
+      <x:c r="AF18" s="36" t="s"/>
+      <x:c r="AG18" s="36" t="s"/>
+      <x:c r="AH18" s="36" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="AI18" s="36" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="AJ18" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AK18" s="36" t="s"/>
+      <x:c r="AL18" s="36" t="s"/>
+      <x:c r="AM18" s="36" t="s"/>
+      <x:c r="AN18" s="36" t="s"/>
+      <x:c r="AO18" s="36" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AP18" s="36" t="s"/>
+      <x:c r="AQ18" s="36" t="s"/>
+      <x:c r="AR18" s="36" t="s"/>
+      <x:c r="AS18" s="36" t="s"/>
+      <x:c r="AT18" s="36" t="s"/>
+      <x:c r="AU18" s="36" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:47" ht="76.5" customHeight="1">
+      <x:c r="A19" s="37" t="s"/>
+      <x:c r="B19" s="35" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C19" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D19" s="36" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E19" s="36" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F19" s="36" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G19" s="36" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H19" s="36" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I19" s="36" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="J19" s="36" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="K19" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L19" s="36" t="s"/>
+      <x:c r="M19" s="36" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="N19" s="36" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="O19" s="36" t="s"/>
+      <x:c r="P19" s="36" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="Q19" s="36" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R19" s="36" t="s"/>
+      <x:c r="S19" s="36" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="T19" s="36" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="U19" s="36" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="V19" s="36" t="s"/>
+      <x:c r="W19" s="36" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="X19" s="36" t="s"/>
+      <x:c r="Y19" s="36" t="s"/>
+      <x:c r="Z19" s="36" t="s"/>
+      <x:c r="AA19" s="36" t="s"/>
+      <x:c r="AB19" s="36" t="s"/>
+      <x:c r="AC19" s="36" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AD19" s="36" t="s"/>
+      <x:c r="AE19" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AF19" s="36" t="s"/>
+      <x:c r="AG19" s="36" t="s"/>
+      <x:c r="AH19" s="36" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="AI19" s="36" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AJ19" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="AK19" s="36" t="s"/>
+      <x:c r="AL19" s="36" t="s"/>
+      <x:c r="AM19" s="36" t="s"/>
+      <x:c r="AN19" s="36" t="s"/>
+      <x:c r="AO19" s="36" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AP19" s="36" t="s"/>
+      <x:c r="AQ19" s="36" t="s"/>
+      <x:c r="AR19" s="36" t="s"/>
+      <x:c r="AS19" s="36" t="s"/>
+      <x:c r="AT19" s="36" t="s"/>
+      <x:c r="AU19" s="36" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:47" ht="89.25" customHeight="1">
+      <x:c r="A20" s="37" t="s"/>
+      <x:c r="B20" s="35" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C20" s="36" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D20" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E20" s="36" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F20" s="36" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G20" s="36" t="s"/>
+      <x:c r="H20" s="36" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="I20" s="36" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="J20" s="36" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="K20" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L20" s="36" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="M20" s="36" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="N20" s="36" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="O20" s="36" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="P20" s="36" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="Q20" s="36" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R20" s="36" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="S20" s="36" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="T20" s="36" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="U20" s="36" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="V20" s="36" t="s"/>
+      <x:c r="W20" s="36" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="X20" s="36" t="s"/>
+      <x:c r="Y20" s="36" t="s"/>
+      <x:c r="Z20" s="36" t="s"/>
+      <x:c r="AA20" s="36" t="s"/>
+      <x:c r="AB20" s="36" t="s"/>
+      <x:c r="AC20" s="36" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AD20" s="36" t="s"/>
+      <x:c r="AE20" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AF20" s="36" t="s"/>
+      <x:c r="AG20" s="36" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AH20" s="36" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="AI20" s="36" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="AJ20" s="36" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="AK20" s="36" t="s"/>
+      <x:c r="AL20" s="36" t="s"/>
+      <x:c r="AM20" s="36" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="AN20" s="36" t="s"/>
+      <x:c r="AO20" s="36" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="AP20" s="36" t="s"/>
+      <x:c r="AQ20" s="36" t="s"/>
+      <x:c r="AR20" s="36" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="AS20" s="36" t="s"/>
+      <x:c r="AT20" s="36" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="AU20" s="36" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:47" ht="89.25" customHeight="1">
+      <x:c r="A21" s="37" t="s"/>
+      <x:c r="B21" s="35" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C21" s="36" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="D21" s="36" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E21" s="36" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F21" s="36" t="s"/>
+      <x:c r="G21" s="36" t="s"/>
+      <x:c r="H21" s="36" t="s"/>
+      <x:c r="I21" s="36" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="L7" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M7" s="34" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="N7" s="34" t="s"/>
-      <x:c r="O7" s="36" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="P7" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="Q7" s="34" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="R7" s="34" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="S7" s="34" t="s">
+      <x:c r="J21" s="36" t="s"/>
+      <x:c r="K21" s="36" t="s"/>
+      <x:c r="L21" s="36" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="M21" s="36" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="N21" s="36" t="s"/>
+      <x:c r="O21" s="36" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="P21" s="36" t="s"/>
+      <x:c r="Q21" s="36" t="s"/>
+      <x:c r="R21" s="36" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="S21" s="36" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="T21" s="36" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="U21" s="36" t="s"/>
+      <x:c r="V21" s="36" t="s"/>
+      <x:c r="W21" s="36" t="s"/>
+      <x:c r="X21" s="36" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Y21" s="36" t="s"/>
+      <x:c r="Z21" s="36" t="s"/>
+      <x:c r="AA21" s="36" t="s"/>
+      <x:c r="AB21" s="36" t="s"/>
+      <x:c r="AC21" s="36" t="s"/>
+      <x:c r="AD21" s="36" t="s"/>
+      <x:c r="AE21" s="36" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="AF21" s="36" t="s"/>
+      <x:c r="AG21" s="36" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AH21" s="36" t="s"/>
+      <x:c r="AI21" s="36" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="AJ21" s="36" t="s"/>
+      <x:c r="AK21" s="36" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="T7" s="34" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="U7" s="34" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="V7" s="34" t="s"/>
-      <x:c r="W7" s="34" t="s"/>
-      <x:c r="X7" s="34" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="Y7" s="34" t="s"/>
-      <x:c r="Z7" s="34" t="s"/>
-      <x:c r="AA7" s="34" t="s"/>
-      <x:c r="AB7" s="34" t="s"/>
-      <x:c r="AC7" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AD7" s="34" t="s"/>
-      <x:c r="AE7" s="34" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="AF7" s="34" t="s"/>
-      <x:c r="AG7" s="34" t="s"/>
-      <x:c r="AH7" s="34" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AI7" s="34" t="s"/>
-      <x:c r="AJ7" s="34" t="s"/>
-      <x:c r="AK7" s="34" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AL7" s="34" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AM7" s="36" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="AN7" s="34" t="s"/>
-      <x:c r="AO7" s="34" t="s"/>
-      <x:c r="AP7" s="34" t="s"/>
-      <x:c r="AQ7" s="34" t="s"/>
-      <x:c r="AR7" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS7" s="34" t="s">
+      <x:c r="AL21" s="36" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="AM21" s="36" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="AT7" s="34" t="s">
+      <x:c r="AN21" s="36" t="s"/>
+      <x:c r="AO21" s="36" t="s"/>
+      <x:c r="AP21" s="36" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AQ21" s="36" t="s"/>
+      <x:c r="AR21" s="36" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="AS21" s="36" t="s"/>
+      <x:c r="AT21" s="36" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="AU21" s="36" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A22" s="37" t="s"/>
+      <x:c r="B22" s="35" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="C22" s="36" t="s"/>
+      <x:c r="D22" s="36" t="s"/>
+      <x:c r="E22" s="36" t="s"/>
+      <x:c r="F22" s="36" t="s"/>
+      <x:c r="G22" s="36" t="s"/>
+      <x:c r="H22" s="36" t="s"/>
+      <x:c r="I22" s="36" t="s"/>
+      <x:c r="J22" s="36" t="s"/>
+      <x:c r="K22" s="36" t="s"/>
+      <x:c r="L22" s="36" t="s"/>
+      <x:c r="M22" s="36" t="s"/>
+      <x:c r="N22" s="36" t="s"/>
+      <x:c r="O22" s="36" t="s"/>
+      <x:c r="P22" s="36" t="s"/>
+      <x:c r="Q22" s="36" t="s"/>
+      <x:c r="R22" s="36" t="s"/>
+      <x:c r="S22" s="36" t="s"/>
+      <x:c r="T22" s="36" t="s"/>
+      <x:c r="U22" s="36" t="s"/>
+      <x:c r="V22" s="36" t="s"/>
+      <x:c r="W22" s="36" t="s"/>
+      <x:c r="X22" s="36" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Y22" s="36" t="s"/>
+      <x:c r="Z22" s="36" t="s"/>
+      <x:c r="AA22" s="36" t="s"/>
+      <x:c r="AB22" s="36" t="s"/>
+      <x:c r="AC22" s="36" t="s"/>
+      <x:c r="AD22" s="36" t="s"/>
+      <x:c r="AE22" s="36" t="s"/>
+      <x:c r="AF22" s="36" t="s"/>
+      <x:c r="AG22" s="36" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="AH22" s="36" t="s"/>
+      <x:c r="AI22" s="36" t="s"/>
+      <x:c r="AJ22" s="36" t="s"/>
+      <x:c r="AK22" s="36" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AL22" s="36" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="AM22" s="36" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="AN22" s="36" t="s"/>
+      <x:c r="AO22" s="36" t="s"/>
+      <x:c r="AP22" s="36" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AQ22" s="36" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="AU7" s="34" t="s">
-        <x:v>88</x:v>
+      <x:c r="AR22" s="36" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AS22" s="36" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="AT22" s="36" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="AU22" s="36" t="s">
+        <x:v>172</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:47" s="7" customFormat="1" ht="79.2" customHeight="1">
-      <x:c r="A8" s="35" t="s"/>
-      <x:c r="B8" s="33" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C8" s="36" t="s">
+    <x:row r="23" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A23" s="37" t="s"/>
+      <x:c r="B23" s="35" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="C23" s="36" t="s"/>
+      <x:c r="D23" s="36" t="s"/>
+      <x:c r="E23" s="36" t="s"/>
+      <x:c r="F23" s="36" t="s"/>
+      <x:c r="G23" s="36" t="s"/>
+      <x:c r="H23" s="36" t="s"/>
+      <x:c r="I23" s="36" t="s"/>
+      <x:c r="J23" s="36" t="s"/>
+      <x:c r="K23" s="36" t="s"/>
+      <x:c r="L23" s="36" t="s"/>
+      <x:c r="M23" s="36" t="s"/>
+      <x:c r="N23" s="36" t="s"/>
+      <x:c r="O23" s="36" t="s"/>
+      <x:c r="P23" s="36" t="s"/>
+      <x:c r="Q23" s="36" t="s"/>
+      <x:c r="R23" s="36" t="s"/>
+      <x:c r="S23" s="36" t="s"/>
+      <x:c r="T23" s="36" t="s"/>
+      <x:c r="U23" s="36" t="s"/>
+      <x:c r="V23" s="36" t="s"/>
+      <x:c r="W23" s="36" t="s"/>
+      <x:c r="X23" s="36" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="Y23" s="36" t="s"/>
+      <x:c r="Z23" s="36" t="s"/>
+      <x:c r="AA23" s="36" t="s"/>
+      <x:c r="AB23" s="36" t="s"/>
+      <x:c r="AC23" s="36" t="s"/>
+      <x:c r="AD23" s="36" t="s"/>
+      <x:c r="AE23" s="36" t="s"/>
+      <x:c r="AF23" s="36" t="s"/>
+      <x:c r="AG23" s="36" t="s"/>
+      <x:c r="AH23" s="36" t="s"/>
+      <x:c r="AI23" s="36" t="s"/>
+      <x:c r="AJ23" s="36" t="s"/>
+      <x:c r="AK23" s="36" t="s"/>
+      <x:c r="AL23" s="36" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="AM23" s="36" t="s"/>
+      <x:c r="AN23" s="36" t="s"/>
+      <x:c r="AO23" s="36" t="s"/>
+      <x:c r="AP23" s="36" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="AQ23" s="36" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="AR23" s="36" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="F8" s="34" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H8" s="34" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="I8" s="34" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J8" s="34" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K8" s="34" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="L8" s="34" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M8" s="34" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="N8" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="O8" s="36" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="P8" s="36" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="Q8" s="34" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="R8" s="34" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="S8" s="34" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="T8" s="34" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="U8" s="34" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="V8" s="34" t="s"/>
-      <x:c r="W8" s="34" t="s"/>
-      <x:c r="X8" s="34" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="Y8" s="34" t="s"/>
-      <x:c r="Z8" s="34" t="s"/>
-      <x:c r="AA8" s="34" t="s"/>
-      <x:c r="AB8" s="34" t="s"/>
-      <x:c r="AC8" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AD8" s="34" t="s"/>
-      <x:c r="AE8" s="34" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="AF8" s="34" t="s"/>
-      <x:c r="AG8" s="34" t="s"/>
-      <x:c r="AH8" s="34" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AI8" s="34" t="s"/>
-      <x:c r="AJ8" s="34" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AK8" s="34" t="s"/>
-      <x:c r="AL8" s="34" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AM8" s="36" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="AN8" s="34" t="s"/>
-      <x:c r="AO8" s="34" t="s"/>
-      <x:c r="AP8" s="34" t="s"/>
-      <x:c r="AQ8" s="34" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="AR8" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS8" s="34" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="AT8" s="34" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AU8" s="34" t="s">
-        <x:v>104</x:v>
+      <x:c r="AS23" s="36" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="AT23" s="36" t="s"/>
+      <x:c r="AU23" s="36" t="s">
+        <x:v>107</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:47" ht="92.4" customHeight="1">
-      <x:c r="A9" s="35" t="s"/>
-      <x:c r="B9" s="33" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C9" s="36" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D9" s="34" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F9" s="34" t="s"/>
-      <x:c r="G9" s="34" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H9" s="34" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="I9" s="34" t="s"/>
-      <x:c r="J9" s="34" t="s"/>
-      <x:c r="K9" s="34" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L9" s="34" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="M9" s="34" t="s"/>
-      <x:c r="N9" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="P9" s="36" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="Q9" s="34" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="R9" s="34" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="S9" s="34" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="T9" s="34" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="U9" s="34" t="s"/>
-      <x:c r="V9" s="34" t="s"/>
-      <x:c r="W9" s="34" t="s"/>
-      <x:c r="X9" s="34" t="s"/>
-      <x:c r="Y9" s="34" t="s"/>
-      <x:c r="Z9" s="34" t="s"/>
-      <x:c r="AA9" s="34" t="s"/>
-      <x:c r="AB9" s="34" t="s"/>
-      <x:c r="AC9" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AD9" s="34" t="s"/>
-      <x:c r="AE9" s="34" t="s"/>
-      <x:c r="AF9" s="34" t="s"/>
-      <x:c r="AG9" s="34" t="s"/>
-      <x:c r="AH9" s="34" t="s"/>
-      <x:c r="AI9" s="34" t="s"/>
-      <x:c r="AJ9" s="34" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="AK9" s="34" t="s"/>
-      <x:c r="AL9" s="34" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="AM9" s="36" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="AN9" s="34" t="s"/>
-      <x:c r="AO9" s="34" t="s"/>
-      <x:c r="AP9" s="34" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AQ9" s="34" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="AR9" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS9" s="34" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AT9" s="34" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="AU9" s="34" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:47" ht="92.4" customHeight="1">
-      <x:c r="A10" s="35" t="s"/>
-      <x:c r="B10" s="33" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C10" s="36" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D10" s="34" t="s"/>
-      <x:c r="E10" s="34" t="s"/>
-      <x:c r="F10" s="34" t="s"/>
-      <x:c r="G10" s="34" t="s"/>
-      <x:c r="H10" s="34" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="I10" s="34" t="s"/>
-      <x:c r="J10" s="34" t="s"/>
-      <x:c r="K10" s="34" t="s"/>
-      <x:c r="L10" s="34" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M10" s="34" t="s"/>
-      <x:c r="N10" s="34" t="s"/>
-      <x:c r="O10" s="36" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="P10" s="36" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="Q10" s="34" t="s"/>
-      <x:c r="R10" s="34" t="s"/>
-      <x:c r="S10" s="34" t="s"/>
-      <x:c r="T10" s="34" t="s"/>
-      <x:c r="U10" s="34" t="s"/>
-      <x:c r="V10" s="34" t="s"/>
-      <x:c r="W10" s="34" t="s"/>
-      <x:c r="X10" s="34" t="s"/>
-      <x:c r="Y10" s="34" t="s"/>
-      <x:c r="Z10" s="34" t="s"/>
-      <x:c r="AA10" s="34" t="s"/>
-      <x:c r="AB10" s="34" t="s"/>
-      <x:c r="AC10" s="34" t="s"/>
-      <x:c r="AD10" s="34" t="s"/>
-      <x:c r="AE10" s="34" t="s"/>
-      <x:c r="AF10" s="34" t="s"/>
-      <x:c r="AG10" s="34" t="s"/>
-      <x:c r="AH10" s="34" t="s"/>
-      <x:c r="AI10" s="34" t="s"/>
-      <x:c r="AJ10" s="34" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="AK10" s="34" t="s"/>
-      <x:c r="AL10" s="34" t="s"/>
-      <x:c r="AM10" s="36" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="AN10" s="34" t="s"/>
-      <x:c r="AO10" s="34" t="s"/>
-      <x:c r="AP10" s="34" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="AQ10" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AR10" s="34" t="s"/>
-      <x:c r="AS10" s="34" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AT10" s="34" t="s"/>
-      <x:c r="AU10" s="34" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A11" s="35" t="s"/>
-      <x:c r="B11" s="33" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C11" s="34" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D11" s="34" t="s"/>
-      <x:c r="E11" s="34" t="s"/>
-      <x:c r="F11" s="34" t="s"/>
-      <x:c r="G11" s="34" t="s"/>
-      <x:c r="H11" s="37" t="s"/>
-      <x:c r="I11" s="34" t="s"/>
-      <x:c r="J11" s="34" t="s"/>
-      <x:c r="K11" s="34" t="s"/>
-      <x:c r="L11" s="34" t="s"/>
-      <x:c r="M11" s="34" t="s"/>
-      <x:c r="N11" s="34" t="s"/>
-      <x:c r="O11" s="36" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="P11" s="36" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="Q11" s="34" t="s"/>
-      <x:c r="R11" s="34" t="s"/>
-      <x:c r="S11" s="34" t="s"/>
-      <x:c r="T11" s="34" t="s"/>
-      <x:c r="U11" s="34" t="s"/>
-      <x:c r="V11" s="34" t="s"/>
-      <x:c r="W11" s="34" t="s"/>
-      <x:c r="X11" s="34" t="s"/>
-      <x:c r="Y11" s="34" t="s"/>
-      <x:c r="Z11" s="34" t="s"/>
-      <x:c r="AA11" s="34" t="s"/>
-      <x:c r="AB11" s="34" t="s"/>
-      <x:c r="AC11" s="34" t="s"/>
-      <x:c r="AD11" s="34" t="s"/>
-      <x:c r="AE11" s="34" t="s"/>
-      <x:c r="AF11" s="34" t="s"/>
-      <x:c r="AG11" s="34" t="s"/>
-      <x:c r="AH11" s="34" t="s"/>
-      <x:c r="AI11" s="34" t="s"/>
-      <x:c r="AJ11" s="34" t="s"/>
-      <x:c r="AK11" s="34" t="s"/>
-      <x:c r="AL11" s="34" t="s"/>
-      <x:c r="AM11" s="34" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="AN11" s="34" t="s"/>
-      <x:c r="AO11" s="34" t="s"/>
-      <x:c r="AP11" s="34" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AQ11" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AR11" s="34" t="s"/>
-      <x:c r="AS11" s="34" t="s"/>
-      <x:c r="AT11" s="34" t="s"/>
-      <x:c r="AU11" s="34" t="s"/>
-    </x:row>
-    <x:row r="12" spans="1:47" ht="79.2" customHeight="1">
-      <x:c r="A12" s="18" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B12" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D12" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H12" s="14" t="s"/>
-      <x:c r="I12" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="J12" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="K12" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="L12" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="N12" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="O12" s="36" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="P12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="Q12" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="R12" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="S12" s="14" t="s"/>
-      <x:c r="T12" s="14" t="s"/>
-      <x:c r="U12" s="14" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="V12" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="W12" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="X12" s="14" t="s"/>
-      <x:c r="Y12" s="14" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="Z12" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AA12" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="AB12" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AC12" s="14" t="s"/>
-      <x:c r="AD12" s="14" t="s"/>
-      <x:c r="AE12" s="14" t="s"/>
-      <x:c r="AF12" s="14" t="s"/>
-      <x:c r="AG12" s="14" t="s"/>
-      <x:c r="AH12" s="14" t="s"/>
-      <x:c r="AI12" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AJ12" s="14" t="s"/>
-      <x:c r="AK12" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AL12" s="14" t="s"/>
-      <x:c r="AM12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="AN12" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AO12" s="14" t="s"/>
-      <x:c r="AP12" s="14" t="s"/>
-      <x:c r="AQ12" s="14" t="s"/>
-      <x:c r="AR12" s="14" t="s"/>
-      <x:c r="AS12" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AT12" s="14" t="s"/>
-      <x:c r="AU12" s="14" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:47" ht="92.4" customHeight="1">
-      <x:c r="A13" s="19" t="s"/>
-      <x:c r="B13" s="13" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D13" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H13" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I13" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="J13" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="K13" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="N13" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="O13" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="P13" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="Q13" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="R13" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="S13" s="14" t="s"/>
-      <x:c r="T13" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="U13" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="V13" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="W13" s="14" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="X13" s="14" t="s"/>
-      <x:c r="Y13" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="Z13" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AA13" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="AB13" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AC13" s="14" t="s"/>
-      <x:c r="AD13" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="AE13" s="14" t="s"/>
-      <x:c r="AF13" s="14" t="s"/>
-      <x:c r="AG13" s="14" t="s"/>
-      <x:c r="AH13" s="14" t="s"/>
-      <x:c r="AI13" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AJ13" s="14" t="s"/>
-      <x:c r="AK13" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AL13" s="14" t="s"/>
-      <x:c r="AM13" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="AN13" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AO13" s="14" t="s"/>
-      <x:c r="AP13" s="14" t="s"/>
-      <x:c r="AQ13" s="14" t="s"/>
-      <x:c r="AR13" s="14" t="s"/>
-      <x:c r="AS13" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AT13" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="AU13" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:47" ht="79.2" customHeight="1">
-      <x:c r="A14" s="19" t="s"/>
-      <x:c r="B14" s="13" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D14" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="H14" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="I14" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="J14" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="K14" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="L14" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="N14" s="14" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O14" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="P14" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="Q14" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="R14" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="S14" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="T14" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="U14" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="V14" s="14" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="W14" s="14" t="s"/>
-      <x:c r="X14" s="14" t="s"/>
-      <x:c r="Y14" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="Z14" s="14" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="AA14" s="14" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="AB14" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AC14" s="14" t="s"/>
-      <x:c r="AD14" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="AE14" s="14" t="s"/>
-      <x:c r="AF14" s="14" t="s"/>
-      <x:c r="AG14" s="14" t="s"/>
-      <x:c r="AH14" s="14" t="s"/>
-      <x:c r="AI14" s="14" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AJ14" s="14" t="s"/>
-      <x:c r="AK14" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AL14" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="AM14" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="AN14" s="14" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AO14" s="14" t="s"/>
-      <x:c r="AP14" s="14" t="s"/>
-      <x:c r="AQ14" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AR14" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="AS14" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AT14" s="14" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="AU14" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A15" s="19" t="s"/>
-      <x:c r="B15" s="13" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="D15" s="14" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s"/>
-      <x:c r="H15" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I15" s="14" t="s"/>
-      <x:c r="J15" s="14" t="s"/>
-      <x:c r="K15" s="14" t="s"/>
-      <x:c r="L15" s="14" t="s"/>
-      <x:c r="M15" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="N15" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="O15" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="P15" s="14" t="s"/>
-      <x:c r="Q15" s="14" t="s"/>
-      <x:c r="R15" s="14" t="s"/>
-      <x:c r="S15" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="T15" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="U15" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="V15" s="14" t="s"/>
-      <x:c r="W15" s="14" t="s"/>
-      <x:c r="X15" s="14" t="s"/>
-      <x:c r="Y15" s="14" t="s"/>
-      <x:c r="Z15" s="14" t="s"/>
-      <x:c r="AA15" s="14" t="s"/>
-      <x:c r="AB15" s="14" t="s"/>
-      <x:c r="AC15" s="14" t="s"/>
-      <x:c r="AD15" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="AE15" s="14" t="s"/>
-      <x:c r="AF15" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AG15" s="14" t="s"/>
-      <x:c r="AH15" s="14" t="s"/>
-      <x:c r="AI15" s="14" t="s"/>
-      <x:c r="AJ15" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AK15" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AL15" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="AM15" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AN15" s="14" t="s"/>
-      <x:c r="AO15" s="14" t="s"/>
-      <x:c r="AP15" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AQ15" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AR15" s="14" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="AS15" s="14" t="s"/>
-      <x:c r="AT15" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="AU15" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A16" s="19" t="s"/>
-      <x:c r="B16" s="13" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s"/>
-      <x:c r="D16" s="14" t="s"/>
-      <x:c r="E16" s="14" t="s"/>
-      <x:c r="F16" s="14" t="s"/>
-      <x:c r="G16" s="14" t="s"/>
-      <x:c r="H16" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I16" s="14" t="s"/>
-      <x:c r="J16" s="14" t="s"/>
-      <x:c r="K16" s="14" t="s"/>
-      <x:c r="L16" s="14" t="s"/>
-      <x:c r="M16" s="14" t="s"/>
-      <x:c r="N16" s="14" t="s"/>
-      <x:c r="O16" s="14" t="s"/>
-      <x:c r="P16" s="14" t="s"/>
-      <x:c r="Q16" s="14" t="s"/>
-      <x:c r="R16" s="14" t="s"/>
-      <x:c r="S16" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="T16" s="14" t="s"/>
-      <x:c r="U16" s="14" t="s"/>
-      <x:c r="V16" s="14" t="s"/>
-      <x:c r="W16" s="14" t="s"/>
-      <x:c r="X16" s="14" t="s"/>
-      <x:c r="Y16" s="14" t="s"/>
-      <x:c r="Z16" s="14" t="s"/>
-      <x:c r="AA16" s="14" t="s"/>
-      <x:c r="AB16" s="14" t="s"/>
-      <x:c r="AC16" s="14" t="s"/>
-      <x:c r="AD16" s="14" t="s"/>
-      <x:c r="AE16" s="14" t="s"/>
-      <x:c r="AF16" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AG16" s="14" t="s"/>
-      <x:c r="AH16" s="14" t="s"/>
-      <x:c r="AI16" s="14" t="s"/>
-      <x:c r="AJ16" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AK16" s="14" t="s"/>
-      <x:c r="AL16" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="AM16" s="14" t="s"/>
-      <x:c r="AN16" s="14" t="s"/>
-      <x:c r="AO16" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="AP16" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="AQ16" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AR16" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS16" s="14" t="s"/>
-      <x:c r="AT16" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AU16" s="14" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A17" s="19" t="s"/>
-      <x:c r="B17" s="13" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s"/>
-      <x:c r="D17" s="14" t="s"/>
-      <x:c r="E17" s="14" t="s"/>
-      <x:c r="F17" s="14" t="s"/>
-      <x:c r="G17" s="14" t="s"/>
-      <x:c r="H17" s="14" t="s"/>
-      <x:c r="I17" s="14" t="s"/>
-      <x:c r="J17" s="14" t="s"/>
-      <x:c r="K17" s="14" t="s"/>
-      <x:c r="L17" s="14" t="s"/>
-      <x:c r="M17" s="14" t="s"/>
-      <x:c r="N17" s="14" t="s"/>
-      <x:c r="O17" s="14" t="s"/>
-      <x:c r="P17" s="14" t="s"/>
-      <x:c r="Q17" s="14" t="s"/>
-      <x:c r="R17" s="14" t="s"/>
-      <x:c r="S17" s="14" t="s"/>
-      <x:c r="T17" s="14" t="s"/>
-      <x:c r="U17" s="14" t="s"/>
-      <x:c r="V17" s="14" t="s"/>
-      <x:c r="W17" s="14" t="s"/>
-      <x:c r="X17" s="14" t="s"/>
-      <x:c r="Y17" s="14" t="s"/>
-      <x:c r="Z17" s="14" t="s"/>
-      <x:c r="AA17" s="14" t="s"/>
-      <x:c r="AB17" s="14" t="s"/>
-      <x:c r="AC17" s="14" t="s"/>
-      <x:c r="AD17" s="14" t="s"/>
-      <x:c r="AE17" s="14" t="s"/>
-      <x:c r="AF17" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AG17" s="14" t="s"/>
-      <x:c r="AH17" s="14" t="s"/>
-      <x:c r="AI17" s="14" t="s"/>
-      <x:c r="AJ17" s="14" t="s"/>
-      <x:c r="AK17" s="14" t="s"/>
-      <x:c r="AL17" s="14" t="s"/>
-      <x:c r="AM17" s="14" t="s"/>
-      <x:c r="AN17" s="14" t="s"/>
-      <x:c r="AO17" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="AP17" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="AQ17" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AR17" s="14" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS17" s="14" t="s"/>
-      <x:c r="AT17" s="14" t="s"/>
-      <x:c r="AU17" s="14" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:47" ht="79.2" customHeight="1">
-      <x:c r="A18" s="32" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="34" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E18" s="34" t="s"/>
-      <x:c r="F18" s="34" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H18" s="34" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I18" s="34" t="s"/>
-      <x:c r="J18" s="34" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="K18" s="34" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="L18" s="34" t="s"/>
-      <x:c r="M18" s="34" t="s"/>
-      <x:c r="N18" s="34" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="s"/>
-      <x:c r="P18" s="34" t="s"/>
-      <x:c r="Q18" s="34" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="R18" s="34" t="s"/>
-      <x:c r="S18" s="34" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="T18" s="34" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="U18" s="34" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="V18" s="34" t="s"/>
-      <x:c r="W18" s="34" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="X18" s="34" t="s"/>
-      <x:c r="Y18" s="34" t="s"/>
-      <x:c r="Z18" s="34" t="s"/>
-      <x:c r="AA18" s="34" t="s"/>
-      <x:c r="AB18" s="34" t="s"/>
-      <x:c r="AC18" s="34" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AD18" s="34" t="s"/>
-      <x:c r="AE18" s="34" t="s"/>
-      <x:c r="AF18" s="34" t="s"/>
-      <x:c r="AG18" s="34" t="s"/>
-      <x:c r="AH18" s="34" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AI18" s="34" t="s"/>
-      <x:c r="AJ18" s="34" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AK18" s="34" t="s"/>
-      <x:c r="AL18" s="34" t="s"/>
-      <x:c r="AM18" s="34" t="s"/>
-      <x:c r="AN18" s="34" t="s"/>
-      <x:c r="AO18" s="34" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AP18" s="34" t="s"/>
-      <x:c r="AQ18" s="34" t="s"/>
-      <x:c r="AR18" s="34" t="s"/>
-      <x:c r="AS18" s="34" t="s"/>
-      <x:c r="AT18" s="34" t="s"/>
-      <x:c r="AU18" s="34" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:47" ht="79.2" customHeight="1">
-      <x:c r="A19" s="35" t="s"/>
-      <x:c r="B19" s="33" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="C19" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D19" s="34" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="E19" s="34" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F19" s="34" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H19" s="34" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I19" s="34" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="J19" s="34" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="K19" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L19" s="34" t="s"/>
-      <x:c r="M19" s="34" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="N19" s="34" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="s"/>
-      <x:c r="P19" s="34" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="Q19" s="34" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="R19" s="34" t="s"/>
-      <x:c r="S19" s="34" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="T19" s="34" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="U19" s="34" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="V19" s="34" t="s"/>
-      <x:c r="W19" s="34" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="X19" s="34" t="s"/>
-      <x:c r="Y19" s="34" t="s"/>
-      <x:c r="Z19" s="34" t="s"/>
-      <x:c r="AA19" s="34" t="s"/>
-      <x:c r="AB19" s="34" t="s"/>
-      <x:c r="AC19" s="34" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AD19" s="34" t="s"/>
-      <x:c r="AE19" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AF19" s="34" t="s"/>
-      <x:c r="AG19" s="34" t="s"/>
-      <x:c r="AH19" s="34" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AI19" s="34" t="s"/>
-      <x:c r="AJ19" s="34" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AK19" s="34" t="s"/>
-      <x:c r="AL19" s="34" t="s"/>
-      <x:c r="AM19" s="34" t="s"/>
-      <x:c r="AN19" s="34" t="s"/>
-      <x:c r="AO19" s="34" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AP19" s="34" t="s"/>
-      <x:c r="AQ19" s="34" t="s"/>
-      <x:c r="AR19" s="34" t="s"/>
-      <x:c r="AS19" s="34" t="s"/>
-      <x:c r="AT19" s="34" t="s"/>
-      <x:c r="AU19" s="34" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:47" ht="92.4" customHeight="1">
-      <x:c r="A20" s="35" t="s"/>
-      <x:c r="B20" s="33" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C20" s="34" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D20" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E20" s="34" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F20" s="34" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="s"/>
-      <x:c r="H20" s="34" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="I20" s="34" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="J20" s="34" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K20" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L20" s="34" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="M20" s="34" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="N20" s="34" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="P20" s="34" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="Q20" s="34" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="R20" s="34" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="S20" s="34" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="T20" s="34" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="U20" s="34" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="V20" s="34" t="s"/>
-      <x:c r="W20" s="34" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="X20" s="34" t="s"/>
-      <x:c r="Y20" s="34" t="s"/>
-      <x:c r="Z20" s="34" t="s"/>
-      <x:c r="AA20" s="34" t="s"/>
-      <x:c r="AB20" s="34" t="s"/>
-      <x:c r="AC20" s="34" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="AD20" s="34" t="s"/>
-      <x:c r="AE20" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AF20" s="34" t="s"/>
-      <x:c r="AG20" s="34" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AH20" s="34" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="AI20" s="34" t="s"/>
-      <x:c r="AJ20" s="34" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="AK20" s="34" t="s"/>
-      <x:c r="AL20" s="34" t="s"/>
-      <x:c r="AM20" s="34" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="AN20" s="34" t="s"/>
-      <x:c r="AO20" s="34" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="AP20" s="34" t="s"/>
-      <x:c r="AQ20" s="34" t="s"/>
-      <x:c r="AR20" s="34" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AS20" s="34" t="s"/>
-      <x:c r="AT20" s="34" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="AU20" s="34" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:47" ht="92.4" customHeight="1">
-      <x:c r="A21" s="35" t="s"/>
-      <x:c r="B21" s="33" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C21" s="34" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D21" s="34" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E21" s="34" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F21" s="34" t="s"/>
-      <x:c r="G21" s="34" t="s"/>
-      <x:c r="H21" s="34" t="s"/>
-      <x:c r="I21" s="34" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J21" s="34" t="s"/>
-      <x:c r="K21" s="34" t="s"/>
-      <x:c r="L21" s="34" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="M21" s="34" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="N21" s="34" t="s"/>
-      <x:c r="O21" s="34" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="P21" s="34" t="s"/>
-      <x:c r="Q21" s="34" t="s"/>
-      <x:c r="R21" s="34" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="S21" s="34" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="T21" s="34" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="U21" s="34" t="s"/>
-      <x:c r="V21" s="34" t="s"/>
-      <x:c r="W21" s="34" t="s"/>
-      <x:c r="X21" s="34" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="Y21" s="34" t="s"/>
-      <x:c r="Z21" s="34" t="s"/>
-      <x:c r="AA21" s="34" t="s"/>
-      <x:c r="AB21" s="34" t="s"/>
-      <x:c r="AC21" s="34" t="s"/>
-      <x:c r="AD21" s="34" t="s"/>
-      <x:c r="AE21" s="34" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="AF21" s="34" t="s"/>
-      <x:c r="AG21" s="34" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AH21" s="34" t="s"/>
-      <x:c r="AI21" s="34" t="s"/>
-      <x:c r="AJ21" s="34" t="s"/>
-      <x:c r="AK21" s="34" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AL21" s="34" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="AM21" s="34" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AN21" s="34" t="s"/>
-      <x:c r="AO21" s="34" t="s"/>
-      <x:c r="AP21" s="34" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AQ21" s="34" t="s"/>
-      <x:c r="AR21" s="34" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AS21" s="34" t="s"/>
-      <x:c r="AT21" s="34" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="AU21" s="34" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A22" s="35" t="s"/>
-      <x:c r="B22" s="33" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="C22" s="34" t="s"/>
-      <x:c r="D22" s="34" t="s"/>
-      <x:c r="E22" s="34" t="s"/>
-      <x:c r="F22" s="34" t="s"/>
-      <x:c r="G22" s="34" t="s"/>
-      <x:c r="H22" s="34" t="s"/>
-      <x:c r="I22" s="34" t="s"/>
-      <x:c r="J22" s="34" t="s"/>
-      <x:c r="K22" s="34" t="s"/>
-      <x:c r="L22" s="34" t="s"/>
-      <x:c r="M22" s="34" t="s"/>
-      <x:c r="N22" s="34" t="s"/>
-      <x:c r="O22" s="34" t="s"/>
-      <x:c r="P22" s="34" t="s"/>
-      <x:c r="Q22" s="34" t="s"/>
-      <x:c r="R22" s="34" t="s"/>
-      <x:c r="S22" s="34" t="s"/>
-      <x:c r="T22" s="34" t="s"/>
-      <x:c r="U22" s="34" t="s"/>
-      <x:c r="V22" s="34" t="s"/>
-      <x:c r="W22" s="34" t="s"/>
-      <x:c r="X22" s="34" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="Y22" s="34" t="s"/>
-      <x:c r="Z22" s="34" t="s"/>
-      <x:c r="AA22" s="34" t="s"/>
-      <x:c r="AB22" s="34" t="s"/>
-      <x:c r="AC22" s="34" t="s"/>
-      <x:c r="AD22" s="34" t="s"/>
-      <x:c r="AE22" s="34" t="s"/>
-      <x:c r="AF22" s="34" t="s"/>
-      <x:c r="AG22" s="34" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AH22" s="34" t="s"/>
-      <x:c r="AI22" s="34" t="s"/>
-      <x:c r="AJ22" s="34" t="s"/>
-      <x:c r="AK22" s="34" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AL22" s="34" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="AM22" s="34" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="AN22" s="34" t="s"/>
-      <x:c r="AO22" s="34" t="s"/>
-      <x:c r="AP22" s="34" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AQ22" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AR22" s="34" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AS22" s="34" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="AT22" s="34" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="AU22" s="34" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A23" s="35" t="s"/>
-      <x:c r="B23" s="33" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C23" s="34" t="s"/>
-      <x:c r="D23" s="34" t="s"/>
-      <x:c r="E23" s="34" t="s"/>
-      <x:c r="F23" s="34" t="s"/>
-      <x:c r="G23" s="34" t="s"/>
-      <x:c r="H23" s="34" t="s"/>
-      <x:c r="I23" s="34" t="s"/>
-      <x:c r="J23" s="34" t="s"/>
-      <x:c r="K23" s="34" t="s"/>
-      <x:c r="L23" s="34" t="s"/>
-      <x:c r="M23" s="34" t="s"/>
-      <x:c r="N23" s="34" t="s"/>
-      <x:c r="O23" s="34" t="s"/>
-      <x:c r="P23" s="34" t="s"/>
-      <x:c r="Q23" s="34" t="s"/>
-      <x:c r="R23" s="34" t="s"/>
-      <x:c r="S23" s="34" t="s"/>
-      <x:c r="T23" s="34" t="s"/>
-      <x:c r="U23" s="34" t="s"/>
-      <x:c r="V23" s="34" t="s"/>
-      <x:c r="W23" s="34" t="s"/>
-      <x:c r="X23" s="34" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="Y23" s="34" t="s"/>
-      <x:c r="Z23" s="34" t="s"/>
-      <x:c r="AA23" s="34" t="s"/>
-      <x:c r="AB23" s="34" t="s"/>
-      <x:c r="AC23" s="34" t="s"/>
-      <x:c r="AD23" s="34" t="s"/>
-      <x:c r="AE23" s="34" t="s"/>
-      <x:c r="AF23" s="34" t="s"/>
-      <x:c r="AG23" s="34" t="s"/>
-      <x:c r="AH23" s="34" t="s"/>
-      <x:c r="AI23" s="34" t="s"/>
-      <x:c r="AJ23" s="34" t="s"/>
-      <x:c r="AK23" s="34" t="s"/>
-      <x:c r="AL23" s="34" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="AM23" s="34" t="s"/>
-      <x:c r="AN23" s="34" t="s"/>
-      <x:c r="AO23" s="34" t="s"/>
-      <x:c r="AP23" s="34" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="AQ23" s="34" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AR23" s="34" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="AS23" s="34" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="AT23" s="34" t="s"/>
-      <x:c r="AU23" s="34" t="s">
-        <x:v>104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:47" ht="53.4" customHeight="1">
-      <x:c r="A24" s="38" t="s"/>
-      <x:c r="B24" s="33" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="C24" s="34" t="s"/>
-      <x:c r="D24" s="34" t="s"/>
-      <x:c r="E24" s="34" t="s"/>
-      <x:c r="F24" s="34" t="s"/>
-      <x:c r="G24" s="34" t="s"/>
-      <x:c r="H24" s="34" t="s"/>
-      <x:c r="I24" s="34" t="s"/>
-      <x:c r="J24" s="34" t="s"/>
-      <x:c r="K24" s="34" t="s"/>
-      <x:c r="L24" s="34" t="s"/>
-      <x:c r="M24" s="34" t="s"/>
-      <x:c r="N24" s="34" t="s"/>
-      <x:c r="O24" s="34" t="s"/>
-      <x:c r="P24" s="34" t="s"/>
-      <x:c r="Q24" s="34" t="s"/>
-      <x:c r="R24" s="34" t="s"/>
-      <x:c r="S24" s="34" t="s"/>
-      <x:c r="T24" s="34" t="s"/>
-      <x:c r="U24" s="34" t="s"/>
-      <x:c r="V24" s="34" t="s"/>
-      <x:c r="W24" s="34" t="s"/>
-      <x:c r="X24" s="34" t="s"/>
-      <x:c r="Y24" s="34" t="s"/>
-      <x:c r="Z24" s="34" t="s"/>
-      <x:c r="AA24" s="34" t="s"/>
-      <x:c r="AB24" s="34" t="s"/>
-      <x:c r="AC24" s="34" t="s"/>
-      <x:c r="AD24" s="34" t="s"/>
-      <x:c r="AE24" s="34" t="s"/>
-      <x:c r="AF24" s="34" t="s"/>
-      <x:c r="AG24" s="34" t="s"/>
-      <x:c r="AH24" s="34" t="s"/>
-      <x:c r="AI24" s="34" t="s"/>
-      <x:c r="AJ24" s="34" t="s"/>
-      <x:c r="AK24" s="34" t="s"/>
-      <x:c r="AL24" s="34" t="s"/>
-      <x:c r="AM24" s="34" t="s"/>
-      <x:c r="AN24" s="34" t="s"/>
-      <x:c r="AO24" s="34" t="s"/>
-      <x:c r="AP24" s="34" t="s"/>
-      <x:c r="AQ24" s="34" t="s"/>
-      <x:c r="AR24" s="34" t="s"/>
-      <x:c r="AS24" s="34" t="s"/>
-      <x:c r="AT24" s="34" t="s"/>
-      <x:c r="AU24" s="34" t="s"/>
+    <x:row r="24" spans="1:47" ht="53.45" customHeight="1">
+      <x:c r="A24" s="42" t="s"/>
+      <x:c r="B24" s="35" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C24" s="36" t="s"/>
+      <x:c r="D24" s="36" t="s"/>
+      <x:c r="E24" s="36" t="s"/>
+      <x:c r="F24" s="36" t="s"/>
+      <x:c r="G24" s="36" t="s"/>
+      <x:c r="H24" s="36" t="s"/>
+      <x:c r="I24" s="36" t="s"/>
+      <x:c r="J24" s="36" t="s"/>
+      <x:c r="K24" s="36" t="s"/>
+      <x:c r="L24" s="36" t="s"/>
+      <x:c r="M24" s="36" t="s"/>
+      <x:c r="N24" s="36" t="s"/>
+      <x:c r="O24" s="36" t="s"/>
+      <x:c r="P24" s="36" t="s"/>
+      <x:c r="Q24" s="36" t="s"/>
+      <x:c r="R24" s="36" t="s"/>
+      <x:c r="S24" s="36" t="s"/>
+      <x:c r="T24" s="36" t="s"/>
+      <x:c r="U24" s="36" t="s"/>
+      <x:c r="V24" s="36" t="s"/>
+      <x:c r="W24" s="36" t="s"/>
+      <x:c r="X24" s="36" t="s"/>
+      <x:c r="Y24" s="36" t="s"/>
+      <x:c r="Z24" s="36" t="s"/>
+      <x:c r="AA24" s="36" t="s"/>
+      <x:c r="AB24" s="36" t="s"/>
+      <x:c r="AC24" s="36" t="s"/>
+      <x:c r="AD24" s="36" t="s"/>
+      <x:c r="AE24" s="36" t="s"/>
+      <x:c r="AF24" s="36" t="s"/>
+      <x:c r="AG24" s="36" t="s"/>
+      <x:c r="AH24" s="36" t="s"/>
+      <x:c r="AI24" s="36" t="s"/>
+      <x:c r="AJ24" s="36" t="s"/>
+      <x:c r="AK24" s="36" t="s"/>
+      <x:c r="AL24" s="36" t="s"/>
+      <x:c r="AM24" s="36" t="s"/>
+      <x:c r="AN24" s="36" t="s"/>
+      <x:c r="AO24" s="36" t="s"/>
+      <x:c r="AP24" s="36" t="s"/>
+      <x:c r="AQ24" s="36" t="s"/>
+      <x:c r="AR24" s="36" t="s"/>
+      <x:c r="AS24" s="36" t="s"/>
+      <x:c r="AT24" s="36" t="s"/>
+      <x:c r="AU24" s="36" t="s"/>
     </x:row>
     <x:row r="25" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A25" s="39" t="s"/>
+      <x:c r="A25" s="43" t="s"/>
     </x:row>
     <x:row r="26" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A26" s="39" t="s"/>
+      <x:c r="A26" s="43" t="s"/>
     </x:row>
     <x:row r="27" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A27" s="39" t="s"/>
+      <x:c r="A27" s="43" t="s"/>
       <x:c r="B27" s="9" t="s"/>
     </x:row>
     <x:row r="28" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A28" s="39" t="s"/>
+      <x:c r="A28" s="43" t="s"/>
     </x:row>
     <x:row r="29" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A29" s="39" t="s"/>
+      <x:c r="A29" s="43" t="s"/>
     </x:row>
     <x:row r="30" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A30" s="39" t="s"/>
+      <x:c r="A30" s="43" t="s"/>
     </x:row>
     <x:row r="31" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A31" s="39" t="s"/>
+      <x:c r="A31" s="43" t="s"/>
     </x:row>
     <x:row r="32" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A32" s="39" t="s"/>
+      <x:c r="A32" s="43" t="s"/>
     </x:row>
     <x:row r="33" spans="1:47" ht="12" customHeight="1">
-      <x:c r="A33" s="39" t="s"/>
+      <x:c r="A33" s="43" t="s"/>
     </x:row>
     <x:row r="34" spans="1:47" ht="12" customHeight="1"/>
     <x:row r="35" spans="1:47" ht="12" customHeight="1"/>
@@ -4590,7 +4489,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{58088ed0-22b8-4d5a-bebd-1201216669fb}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{71cf6655-54fb-42a5-8485-ca2f4f3e344c}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -4598,8 +4497,8 @@
   <x:sheetFormatPr defaultRowHeight="12.75"/>
   <x:sheetData>
     <x:row r="5" spans="1:1" ht="23.25" customHeight="1">
-      <x:c r="A5" s="40" t="s">
-        <x:v>197</x:v>
+      <x:c r="A5" s="44" t="s">
+        <x:v>202</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
